--- a/AfterToken/Configs/GameConfig/Datas/item.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,21 @@
           <t>exchangeList</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>itemType</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>stackLimit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +534,21 @@
           <t>(list#sep=;),cfg.ItemExchange</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>cfg.EItemType</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +599,21 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>兑换列表</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>道具类型</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>堆叠上限</t>
         </is>
       </c>
     </row>
@@ -591,7 +636,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -604,6 +649,14 @@
         <is>
           <t>10001,2</t>
         </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +678,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -638,6 +691,14 @@
         <is>
           <t>10001,2;10002,3</t>
         </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -659,7 +720,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -672,6 +733,56 @@
         <is>
           <t>10001,2;10002,3;10003,1</t>
         </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>10003</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>王者之剑</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>传说材料</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10001,1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/item.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/item.xlsx
@@ -623,12 +623,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新手剑</t>
+          <t>Novice Sword</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>初始武器</t>
+          <t>A basic sword for beginners.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -665,12 +665,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>Iron Sword</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>进阶武器</t>
+          <t>A sturdy iron blade.</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -707,12 +707,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>钢剑</t>
+          <t>Steel Sword</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>高级武器</t>
+          <t>A refined steel weapon.</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -749,12 +749,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>王者之剑</t>
+          <t>King's Sword</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>传说材料</t>
+          <t>A legendary crafting material.</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/AfterToken/Configs/GameConfig/Datas/item.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,221 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>10004</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Basic building material.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>icon_item_wood</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>10005</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Common construction material.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>icon_item_stone</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>10006</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Freshly harvested wheat.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>icon_item_wheat</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>10007</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A medicinal herb.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>icon_item_herb</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>10008</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Healing Potion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Restores health.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>icon_item_potion</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
